--- a/Shared/XLS/Material.xlsx
+++ b/Shared/XLS/Material.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -64,18 +64,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>재료1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>룬1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Rune</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>MaterialType</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -96,10 +84,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>레이드던전</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>장비던전</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -108,10 +92,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>Source</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>드롭, 상점 구매, 제작, 분해</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -121,6 +101,42 @@
   </si>
   <si>
     <t>Material</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Navigation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 강화에 사용한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 초월에 사용한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검의 첫번째 재료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검의 두번째 재료</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -583,7 +599,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -609,22 +625,17 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
@@ -672,26 +683,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="25.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -700,13 +712,16 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -715,69 +730,88 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="1">
-        <v>60001</v>
+        <v>10001</v>
       </c>
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>12</v>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="1">
-        <v>60002</v>
+        <v>20002</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>12</v>
+      <c r="D5" t="s">
+        <v>22</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
-        <v>60003</v>
+        <v>30003</v>
       </c>
       <c r="C6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
-        <v>60004</v>
+        <v>30004</v>
       </c>
       <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="F7" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8"/>
+      <c r="D8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Shared/XLS/Material.xlsx
+++ b/Shared/XLS/Material.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -100,43 +100,51 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>Navigation</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 강화에 사용한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>장비 초월에 사용한다.</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검의 첫번째 재료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>재료2</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>철검의 두번째 재료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!string</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>Material</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Navigation</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Desc</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>!string</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 강화에 사용한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>장비 초월에 사용한다.</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료1</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검의 첫번째 재료</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>재료2</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>철검의 두번째 재료</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -599,7 +607,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -683,27 +691,28 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" style="9"/>
     <col min="2" max="2" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="5" max="5" width="21.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="8"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
@@ -712,16 +721,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="8"/>
       <c r="B3" s="1" t="s">
         <v>4</v>
@@ -730,16 +742,19 @@
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="8"/>
       <c r="B4" s="1">
         <v>10001</v>
@@ -748,16 +763,17 @@
         <v>6</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="8"/>
       <c r="B5" s="1">
         <v>20002</v>
@@ -766,52 +782,56 @@
         <v>7</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5"/>
+      <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" s="1">
         <v>30003</v>
       </c>
       <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6"/>
+      <c r="F6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="G6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>30004</v>
       </c>
       <c r="C7" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" t="s">
-        <v>26</v>
-      </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7"/>
+      <c r="F7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="C8"/>
       <c r="D8"/>
+      <c r="E8"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Shared/XLS/Material.xlsx
+++ b/Shared/XLS/Material.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -145,6 +145,25 @@
   </si>
   <si>
     <t>Material</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬카드 강화재료1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬카드 강화 재료</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Enchant</t>
+  </si>
+  <si>
+    <t>Enchant</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>모든 던전</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -607,7 +626,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -638,7 +657,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
@@ -829,9 +848,22 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="C8"/>
-      <c r="D8"/>
+      <c r="B8" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C8" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
       <c r="E8"/>
+      <c r="F8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/Shared/XLS/Material.xlsx
+++ b/Shared/XLS/Material.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -164,6 +164,50 @@
   </si>
   <si>
     <t>모든 던전</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaterialGradeType</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Magic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rare</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Epic</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Legendary</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>!MaterialGradeType</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석2</t>
+  </si>
+  <si>
+    <t>강화석3</t>
+  </si>
+  <si>
+    <t>강화석4</t>
+  </si>
+  <si>
+    <t>강화석5</t>
+  </si>
+  <si>
+    <t>MaterialGrade</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -171,7 +215,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -206,14 +250,6 @@
       <sz val="8"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
@@ -316,7 +352,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -326,7 +362,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -344,6 +379,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -638,7 +676,7 @@
   <dimension ref="A1:D18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="8" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.125" style="1" customWidth="1"/>
     <col min="3" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="34.75" style="1" bestFit="1" customWidth="1"/>
@@ -648,7 +686,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
@@ -665,18 +703,39 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B6" s="10" t="s">
+        <v>35</v>
+      </c>
+    </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="3"/>
+      <c r="B7" s="10" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8"/>
+      <c r="B8" s="10" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B9"/>
-      <c r="D9" s="5"/>
+      <c r="B9" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="4"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B10" s="3"/>
+      <c r="B10" s="10" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B11"/>
@@ -710,29 +769,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="9"/>
+    <col min="1" max="1" width="9" style="8"/>
     <col min="2" max="2" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="19" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="8"/>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="7"/>
       <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
@@ -748,12 +808,15 @@
       <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="8"/>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="7"/>
       <c r="B3" s="1" t="s">
         <v>4</v>
       </c>
@@ -769,12 +832,15 @@
       <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="8"/>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7"/>
       <c r="B4" s="1">
         <v>10001</v>
       </c>
@@ -788,80 +854,171 @@
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="8"/>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="7"/>
       <c r="B5" s="1">
-        <v>20002</v>
+        <v>10002</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5"/>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G5" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="7"/>
       <c r="B6" s="1">
-        <v>30003</v>
+        <v>10003</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="7"/>
       <c r="B7" s="1">
-        <v>30004</v>
+        <v>10004</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E7"/>
       <c r="F7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="7"/>
       <c r="B8" s="1">
-        <v>40001</v>
+        <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E8"/>
       <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="7"/>
+      <c r="B9" s="1">
+        <v>20002</v>
+      </c>
+      <c r="C9" t="s">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B10" s="1">
+        <v>30003</v>
+      </c>
+      <c r="C10" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10"/>
+      <c r="F10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B11" s="1">
+        <v>30004</v>
+      </c>
+      <c r="C11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11"/>
+      <c r="F11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B12" s="1">
+        <v>40001</v>
+      </c>
+      <c r="C12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12"/>
+      <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G12" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>33</v>
       </c>
     </row>

--- a/Shared/XLS/Material.xlsx
+++ b/Shared/XLS/Material.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="51">
   <si>
     <t>!Enum</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -191,23 +191,40 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>강화석2</t>
+  </si>
+  <si>
+    <t>강화석3</t>
+  </si>
+  <si>
+    <t>강화석4</t>
+  </si>
+  <si>
+    <t>강화석5</t>
+  </si>
+  <si>
+    <t>MaterialGrade</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_GemStone_Red</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Triangle_Green</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Meat</t>
+  </si>
+  <si>
+    <t>ItemIcon_Clover</t>
+  </si>
+  <si>
+    <t>Icon_Potion</t>
+  </si>
+  <si>
     <t>!MaterialGradeType</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석2</t>
-  </si>
-  <si>
-    <t>강화석3</t>
-  </si>
-  <si>
-    <t>강화석4</t>
-  </si>
-  <si>
-    <t>강화석5</t>
-  </si>
-  <si>
-    <t>MaterialGrade</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -664,7 +681,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -776,7 +793,7 @@
     <col min="2" max="2" width="14.625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.25" style="1" customWidth="1"/>
     <col min="4" max="4" width="21.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="29" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.375" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="19" style="1" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.375" style="1" bestFit="1" customWidth="1"/>
@@ -809,7 +826,7 @@
         <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>17</v>
@@ -833,7 +850,7 @@
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>12</v>
@@ -850,7 +867,9 @@
       <c r="D4" t="s">
         <v>20</v>
       </c>
-      <c r="E4"/>
+      <c r="E4" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F4" s="1" t="s">
         <v>9</v>
       </c>
@@ -867,12 +886,14 @@
         <v>10002</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
         <v>20</v>
       </c>
-      <c r="E5"/>
+      <c r="E5" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
@@ -886,12 +907,14 @@
         <v>10003</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
         <v>20</v>
       </c>
-      <c r="E6"/>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F6" s="1" t="s">
         <v>9</v>
       </c>
@@ -905,12 +928,14 @@
         <v>10004</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="E7"/>
+      <c r="E7" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
@@ -924,12 +949,14 @@
         <v>10005</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D8" t="s">
         <v>20</v>
       </c>
-      <c r="E8"/>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
       <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
@@ -948,7 +975,9 @@
       <c r="D9" t="s">
         <v>21</v>
       </c>
-      <c r="E9"/>
+      <c r="E9" s="1" t="s">
+        <v>46</v>
+      </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
@@ -969,7 +998,9 @@
       <c r="D10" t="s">
         <v>23</v>
       </c>
-      <c r="E10"/>
+      <c r="E10" s="1" t="s">
+        <v>47</v>
+      </c>
       <c r="F10" s="1" t="s">
         <v>16</v>
       </c>
@@ -990,7 +1021,9 @@
       <c r="D11" t="s">
         <v>25</v>
       </c>
-      <c r="E11"/>
+      <c r="E11" s="1" t="s">
+        <v>48</v>
+      </c>
       <c r="F11" s="1" t="s">
         <v>16</v>
       </c>
@@ -1011,7 +1044,9 @@
       <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c r="E12"/>
+      <c r="E12" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="F12" s="1" t="s">
         <v>31</v>
       </c>
